--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124257002</v>
+        <v>124255681</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -833,14 +833,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498588</v>
+        <v>498428</v>
       </c>
       <c r="R3" t="n">
-        <v>6909664</v>
+        <v>6910043</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124255787</v>
+        <v>124256321</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498444</v>
+        <v>498379</v>
       </c>
       <c r="R5" t="n">
-        <v>6910034</v>
+        <v>6909903</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124255822</v>
+        <v>124256127</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,25 +1133,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498423</v>
+        <v>498375</v>
       </c>
       <c r="R6" t="n">
-        <v>6910002</v>
+        <v>6909917</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124256127</v>
+        <v>124256105</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,25 +1235,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498375</v>
+        <v>498395</v>
       </c>
       <c r="R7" t="n">
-        <v>6909917</v>
+        <v>6909922</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124256885</v>
+        <v>124258627</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,37 +1341,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498538</v>
+        <v>498669</v>
       </c>
       <c r="R8" t="n">
-        <v>6909687</v>
+        <v>6909943</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124255681</v>
+        <v>124257002</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1462,7 +1467,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1472,14 +1477,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498428</v>
+        <v>498588</v>
       </c>
       <c r="R9" t="n">
-        <v>6910043</v>
+        <v>6909664</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124258627</v>
+        <v>124257030</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,46 +1555,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498669</v>
+        <v>498590</v>
       </c>
       <c r="R10" t="n">
-        <v>6909943</v>
+        <v>6909676</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124256321</v>
+        <v>124255822</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,47 +1666,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498379</v>
+        <v>498423</v>
       </c>
       <c r="R11" t="n">
-        <v>6909903</v>
+        <v>6910002</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124258267</v>
+        <v>124255787</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,38 +1768,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498730</v>
+        <v>498444</v>
       </c>
       <c r="R12" t="n">
-        <v>6909760</v>
+        <v>6910034</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1858,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124257030</v>
+        <v>124258047</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,35 +1879,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1907,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498590</v>
+        <v>498617</v>
       </c>
       <c r="R13" t="n">
-        <v>6909676</v>
+        <v>6909667</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1969,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124257082</v>
+        <v>124258267</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,47 +1991,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498617</v>
+        <v>498730</v>
       </c>
       <c r="R14" t="n">
-        <v>6909667</v>
+        <v>6909760</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2080,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124256105</v>
+        <v>124256885</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2120,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498395</v>
+        <v>498538</v>
       </c>
       <c r="R15" t="n">
-        <v>6909922</v>
+        <v>6909687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2182,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124258047</v>
+        <v>124257082</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,36 +2195,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124255681</v>
+        <v>124256885</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,47 +800,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498428</v>
+        <v>498538</v>
       </c>
       <c r="R3" t="n">
-        <v>6910043</v>
+        <v>6909687</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124255718</v>
+        <v>124256321</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -934,7 +925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498428</v>
+        <v>498379</v>
       </c>
       <c r="R4" t="n">
-        <v>6910028</v>
+        <v>6909903</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124256321</v>
+        <v>124257030</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1045,7 +1036,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,14 +1046,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498379</v>
+        <v>498590</v>
       </c>
       <c r="R5" t="n">
-        <v>6909903</v>
+        <v>6909676</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1223,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124256105</v>
+        <v>124258627</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,37 +1230,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498395</v>
+        <v>498669</v>
       </c>
       <c r="R7" t="n">
-        <v>6909922</v>
+        <v>6909943</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124258627</v>
+        <v>124255787</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,31 +1333,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498669</v>
+        <v>498444</v>
       </c>
       <c r="R8" t="n">
-        <v>6909943</v>
+        <v>6910034</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124257002</v>
+        <v>124256105</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,47 +1444,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498588</v>
+        <v>498395</v>
       </c>
       <c r="R9" t="n">
-        <v>6909664</v>
+        <v>6909922</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1543,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124257030</v>
+        <v>124255822</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,47 +1546,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498590</v>
+        <v>498423</v>
       </c>
       <c r="R10" t="n">
-        <v>6909676</v>
+        <v>6910002</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124255822</v>
+        <v>124258047</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,34 +1652,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498423</v>
+        <v>498617</v>
       </c>
       <c r="R11" t="n">
-        <v>6910002</v>
+        <v>6909667</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1748,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124255787</v>
+        <v>124255681</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1791,7 +1783,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1805,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498444</v>
+        <v>498428</v>
       </c>
       <c r="R12" t="n">
-        <v>6910034</v>
+        <v>6910043</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1867,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124258047</v>
+        <v>124258267</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,44 +1875,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498617</v>
+        <v>498730</v>
       </c>
       <c r="R13" t="n">
-        <v>6909667</v>
+        <v>6909760</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1979,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124258267</v>
+        <v>124257002</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,38 +1973,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498730</v>
+        <v>498588</v>
       </c>
       <c r="R14" t="n">
-        <v>6909760</v>
+        <v>6909664</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124256885</v>
+        <v>124255718</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,38 +2084,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498538</v>
+        <v>498428</v>
       </c>
       <c r="R15" t="n">
-        <v>6909687</v>
+        <v>6910028</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124256885</v>
+        <v>124258267</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -824,14 +824,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498538</v>
+        <v>498730</v>
       </c>
       <c r="R3" t="n">
-        <v>6909687</v>
+        <v>6909760</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124256321</v>
+        <v>124256127</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -923,26 +923,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498379</v>
+        <v>498375</v>
       </c>
       <c r="R4" t="n">
-        <v>6909903</v>
+        <v>6909917</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124257030</v>
+        <v>124258627</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,50 +1004,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498590</v>
+        <v>498669</v>
       </c>
       <c r="R5" t="n">
-        <v>6909676</v>
+        <v>6909943</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124256127</v>
+        <v>124255822</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498375</v>
+        <v>498423</v>
       </c>
       <c r="R6" t="n">
-        <v>6909917</v>
+        <v>6910002</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124258627</v>
+        <v>124256321</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,31 +1213,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1259,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498669</v>
+        <v>498379</v>
       </c>
       <c r="R7" t="n">
-        <v>6909943</v>
+        <v>6909903</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1432,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124256105</v>
+        <v>124257030</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,38 +1435,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498395</v>
+        <v>498590</v>
       </c>
       <c r="R9" t="n">
-        <v>6909922</v>
+        <v>6909676</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124255822</v>
+        <v>124258047</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,34 +1550,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498423</v>
+        <v>498617</v>
       </c>
       <c r="R10" t="n">
-        <v>6910002</v>
+        <v>6909667</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1636,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124258047</v>
+        <v>124257082</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,36 +1658,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1748,7 +1757,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124255681</v>
+        <v>124255718</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1783,7 +1792,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1800,7 +1809,7 @@
         <v>498428</v>
       </c>
       <c r="R12" t="n">
-        <v>6910043</v>
+        <v>6910028</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,7 +1868,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124258267</v>
+        <v>124256885</v>
       </c>
       <c r="B13" t="n">
         <v>79891</v>
@@ -1895,14 +1904,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498730</v>
+        <v>498538</v>
       </c>
       <c r="R13" t="n">
-        <v>6909760</v>
+        <v>6909687</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1961,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124257002</v>
+        <v>124256105</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,47 +1982,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498588</v>
+        <v>498395</v>
       </c>
       <c r="R14" t="n">
-        <v>6909664</v>
+        <v>6909922</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124255718</v>
+        <v>124255681</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>498428</v>
       </c>
       <c r="R15" t="n">
-        <v>6910028</v>
+        <v>6910043</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124257082</v>
+        <v>124257002</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498617</v>
+        <v>498588</v>
       </c>
       <c r="R16" t="n">
-        <v>6909667</v>
+        <v>6909664</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124258267</v>
+        <v>124258047</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,34 +804,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498730</v>
+        <v>498617</v>
       </c>
       <c r="R3" t="n">
-        <v>6909760</v>
+        <v>6909667</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124256127</v>
+        <v>124255822</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498375</v>
+        <v>498423</v>
       </c>
       <c r="R4" t="n">
-        <v>6909917</v>
+        <v>6910002</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124258627</v>
+        <v>124256105</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,42 +1018,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498669</v>
+        <v>498395</v>
       </c>
       <c r="R5" t="n">
-        <v>6909943</v>
+        <v>6909922</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124255822</v>
+        <v>124255718</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1116,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498423</v>
+        <v>498428</v>
       </c>
       <c r="R6" t="n">
-        <v>6910002</v>
+        <v>6910028</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124256321</v>
+        <v>124256885</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1213,47 +1227,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498379</v>
+        <v>498538</v>
       </c>
       <c r="R7" t="n">
-        <v>6909903</v>
+        <v>6909687</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124255787</v>
+        <v>124257002</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1347,7 +1352,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1357,14 +1362,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498444</v>
+        <v>498588</v>
       </c>
       <c r="R8" t="n">
-        <v>6910034</v>
+        <v>6909664</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124257030</v>
+        <v>124258267</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,47 +1440,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498590</v>
+        <v>498730</v>
       </c>
       <c r="R9" t="n">
-        <v>6909676</v>
+        <v>6909760</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124258047</v>
+        <v>124255787</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,48 +1542,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498617</v>
+        <v>498444</v>
       </c>
       <c r="R10" t="n">
-        <v>6909667</v>
+        <v>6910034</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1646,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124257082</v>
+        <v>124257030</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1681,7 +1676,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498617</v>
+        <v>498590</v>
       </c>
       <c r="R11" t="n">
-        <v>6909667</v>
+        <v>6909676</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1757,7 +1752,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124255718</v>
+        <v>124256321</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1792,7 +1787,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1806,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498428</v>
+        <v>498379</v>
       </c>
       <c r="R12" t="n">
-        <v>6910028</v>
+        <v>6909903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124256885</v>
+        <v>124258627</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,37 +1879,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498538</v>
+        <v>498669</v>
       </c>
       <c r="R13" t="n">
-        <v>6909687</v>
+        <v>6909943</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124256105</v>
+        <v>124256127</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,25 +1982,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498395</v>
+        <v>498375</v>
       </c>
       <c r="R14" t="n">
-        <v>6909922</v>
+        <v>6909917</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124255681</v>
+        <v>124257082</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2117,14 +2117,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498428</v>
+        <v>498617</v>
       </c>
       <c r="R15" t="n">
-        <v>6910043</v>
+        <v>6909667</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124257002</v>
+        <v>124255681</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2228,14 +2228,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498588</v>
+        <v>498428</v>
       </c>
       <c r="R16" t="n">
-        <v>6909664</v>
+        <v>6910043</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124255822</v>
+        <v>124256105</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498423</v>
+        <v>498395</v>
       </c>
       <c r="R4" t="n">
-        <v>6910002</v>
+        <v>6909922</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124256105</v>
+        <v>124255822</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498395</v>
+        <v>498423</v>
       </c>
       <c r="R5" t="n">
-        <v>6909922</v>
+        <v>6910002</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124255718</v>
+        <v>124256885</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,47 +1116,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498428</v>
+        <v>498538</v>
       </c>
       <c r="R6" t="n">
-        <v>6910028</v>
+        <v>6909687</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124256885</v>
+        <v>124255718</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,38 +1218,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498538</v>
+        <v>498428</v>
       </c>
       <c r="R7" t="n">
-        <v>6909687</v>
+        <v>6910028</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124258047</v>
+        <v>124258267</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,44 +804,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498617</v>
+        <v>498730</v>
       </c>
       <c r="R3" t="n">
-        <v>6909667</v>
+        <v>6909760</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124256105</v>
+        <v>124257030</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,38 +902,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498395</v>
+        <v>498590</v>
       </c>
       <c r="R4" t="n">
-        <v>6909922</v>
+        <v>6909676</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124255822</v>
+        <v>124256321</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,38 +1013,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498423</v>
+        <v>498379</v>
       </c>
       <c r="R5" t="n">
-        <v>6910002</v>
+        <v>6909903</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124256885</v>
+        <v>124258627</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,37 +1128,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498538</v>
+        <v>498669</v>
       </c>
       <c r="R6" t="n">
-        <v>6909687</v>
+        <v>6909943</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124255718</v>
+        <v>124256885</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,47 +1231,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498428</v>
+        <v>498538</v>
       </c>
       <c r="R7" t="n">
-        <v>6910028</v>
+        <v>6909687</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124257002</v>
+        <v>124256105</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,47 +1333,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498588</v>
+        <v>498395</v>
       </c>
       <c r="R8" t="n">
-        <v>6909664</v>
+        <v>6909922</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124258267</v>
+        <v>124255822</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1464,14 +1459,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498730</v>
+        <v>498423</v>
       </c>
       <c r="R9" t="n">
-        <v>6909760</v>
+        <v>6910002</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124255787</v>
+        <v>124258047</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,47 +1537,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498444</v>
+        <v>498617</v>
       </c>
       <c r="R10" t="n">
-        <v>6910034</v>
+        <v>6909667</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1637,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124257030</v>
+        <v>124255787</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1676,7 +1672,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1686,14 +1682,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498590</v>
+        <v>498444</v>
       </c>
       <c r="R11" t="n">
-        <v>6909676</v>
+        <v>6910034</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1752,7 +1748,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124256321</v>
+        <v>124255681</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1801,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498379</v>
+        <v>498428</v>
       </c>
       <c r="R12" t="n">
-        <v>6909903</v>
+        <v>6910043</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124258627</v>
+        <v>124257002</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,46 +1871,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498669</v>
+        <v>498588</v>
       </c>
       <c r="R13" t="n">
-        <v>6909943</v>
+        <v>6909664</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124255681</v>
+        <v>124255718</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2235,7 +2235,7 @@
         <v>498428</v>
       </c>
       <c r="R16" t="n">
-        <v>6910043</v>
+        <v>6910028</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124258267</v>
+        <v>124256105</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,34 +804,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498730</v>
+        <v>498395</v>
       </c>
       <c r="R3" t="n">
-        <v>6909760</v>
+        <v>6909922</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124256321</v>
+        <v>124258627</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,35 +1013,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1050,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498379</v>
+        <v>498669</v>
       </c>
       <c r="R5" t="n">
-        <v>6909903</v>
+        <v>6909943</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124258627</v>
+        <v>124256321</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,31 +1120,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498669</v>
+        <v>498379</v>
       </c>
       <c r="R6" t="n">
-        <v>6909943</v>
+        <v>6909903</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124256885</v>
+        <v>124255718</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,38 +1231,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498538</v>
+        <v>498428</v>
       </c>
       <c r="R7" t="n">
-        <v>6909687</v>
+        <v>6910028</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124256105</v>
+        <v>124257002</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,38 +1342,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498395</v>
+        <v>498588</v>
       </c>
       <c r="R8" t="n">
-        <v>6909922</v>
+        <v>6909664</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1525,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124258047</v>
+        <v>124255681</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,48 +1555,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498617</v>
+        <v>498428</v>
       </c>
       <c r="R10" t="n">
-        <v>6909667</v>
+        <v>6910043</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124255787</v>
+        <v>124258267</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,47 +1666,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498444</v>
+        <v>498730</v>
       </c>
       <c r="R11" t="n">
-        <v>6910034</v>
+        <v>6909760</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124255681</v>
+        <v>124255787</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1783,7 +1791,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1797,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498428</v>
+        <v>498444</v>
       </c>
       <c r="R12" t="n">
-        <v>6910043</v>
+        <v>6910034</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124257002</v>
+        <v>124256127</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1892,26 +1900,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498588</v>
+        <v>498375</v>
       </c>
       <c r="R13" t="n">
-        <v>6909664</v>
+        <v>6909917</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124256127</v>
+        <v>124258047</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,38 +1981,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498375</v>
+        <v>498617</v>
       </c>
       <c r="R14" t="n">
-        <v>6909917</v>
+        <v>6909667</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2072,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124257082</v>
+        <v>124256885</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,47 +2093,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498617</v>
+        <v>498538</v>
       </c>
       <c r="R15" t="n">
-        <v>6909667</v>
+        <v>6909687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124255718</v>
+        <v>124257082</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2228,14 +2228,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498428</v>
+        <v>498617</v>
       </c>
       <c r="R16" t="n">
-        <v>6910028</v>
+        <v>6909667</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124256105</v>
+        <v>124257082</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,38 +800,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498395</v>
+        <v>498617</v>
       </c>
       <c r="R3" t="n">
-        <v>6909922</v>
+        <v>6909667</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124257030</v>
+        <v>124256885</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,47 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498590</v>
+        <v>498538</v>
       </c>
       <c r="R4" t="n">
-        <v>6909676</v>
+        <v>6909687</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124258627</v>
+        <v>124255822</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,42 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498669</v>
+        <v>498423</v>
       </c>
       <c r="R5" t="n">
-        <v>6909943</v>
+        <v>6910002</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124256321</v>
+        <v>124256105</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,47 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498379</v>
+        <v>498395</v>
       </c>
       <c r="R6" t="n">
-        <v>6909903</v>
+        <v>6909922</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124255718</v>
+        <v>124258047</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,47 +1217,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498428</v>
+        <v>498617</v>
       </c>
       <c r="R7" t="n">
-        <v>6910028</v>
+        <v>6909667</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124257002</v>
+        <v>124258627</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,50 +1329,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498588</v>
+        <v>498669</v>
       </c>
       <c r="R8" t="n">
-        <v>6909664</v>
+        <v>6909943</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124255822</v>
+        <v>124256127</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,25 +1436,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498423</v>
+        <v>498375</v>
       </c>
       <c r="R9" t="n">
-        <v>6910002</v>
+        <v>6909917</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1543,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124255681</v>
+        <v>124255718</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1578,7 +1561,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1595,7 +1578,7 @@
         <v>498428</v>
       </c>
       <c r="R10" t="n">
-        <v>6910043</v>
+        <v>6910028</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124258267</v>
+        <v>124257030</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,38 +1649,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498730</v>
+        <v>498590</v>
       </c>
       <c r="R11" t="n">
-        <v>6909760</v>
+        <v>6909676</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1748,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124255787</v>
+        <v>124256321</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1791,7 +1783,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1805,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498444</v>
+        <v>498379</v>
       </c>
       <c r="R12" t="n">
-        <v>6910034</v>
+        <v>6909903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1867,7 +1859,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124256127</v>
+        <v>124255681</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1900,17 +1892,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498375</v>
+        <v>498428</v>
       </c>
       <c r="R13" t="n">
-        <v>6909917</v>
+        <v>6910043</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1969,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124258047</v>
+        <v>124258267</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,44 +1986,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498617</v>
+        <v>498730</v>
       </c>
       <c r="R14" t="n">
-        <v>6909667</v>
+        <v>6909760</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124256885</v>
+        <v>124257002</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,38 +2084,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498538</v>
+        <v>498588</v>
       </c>
       <c r="R15" t="n">
-        <v>6909687</v>
+        <v>6909664</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124257082</v>
+        <v>124255787</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2228,14 +2228,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498617</v>
+        <v>498444</v>
       </c>
       <c r="R16" t="n">
-        <v>6909667</v>
+        <v>6910034</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124258627</v>
+        <v>124255718</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,31 +1329,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1362,13 +1366,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498669</v>
+        <v>498428</v>
       </c>
       <c r="R8" t="n">
-        <v>6909943</v>
+        <v>6910028</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1526,7 +1530,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124255718</v>
+        <v>124256321</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1561,7 +1565,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1575,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498428</v>
+        <v>498379</v>
       </c>
       <c r="R10" t="n">
-        <v>6910028</v>
+        <v>6909903</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124257030</v>
+        <v>124258627</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,50 +1653,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498590</v>
+        <v>498669</v>
       </c>
       <c r="R11" t="n">
-        <v>6909676</v>
+        <v>6909943</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124256321</v>
+        <v>124257030</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1793,14 +1793,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498379</v>
+        <v>498590</v>
       </c>
       <c r="R12" t="n">
-        <v>6909903</v>
+        <v>6909676</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124257082</v>
+        <v>124258627</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,50 +800,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498617</v>
+        <v>498669</v>
       </c>
       <c r="R3" t="n">
-        <v>6909667</v>
+        <v>6909943</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124256885</v>
+        <v>124257002</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +907,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498538</v>
+        <v>498588</v>
       </c>
       <c r="R4" t="n">
-        <v>6909687</v>
+        <v>6909664</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124255822</v>
+        <v>124258267</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1037,14 +1042,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498423</v>
+        <v>498730</v>
       </c>
       <c r="R5" t="n">
-        <v>6910002</v>
+        <v>6909760</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124256105</v>
+        <v>124257030</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,38 +1120,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498395</v>
+        <v>498590</v>
       </c>
       <c r="R6" t="n">
-        <v>6909922</v>
+        <v>6909676</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124258047</v>
+        <v>124256885</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,44 +1235,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498617</v>
+        <v>498538</v>
       </c>
       <c r="R7" t="n">
-        <v>6909667</v>
+        <v>6909687</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124255718</v>
+        <v>124256105</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,47 +1333,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498428</v>
+        <v>498395</v>
       </c>
       <c r="R8" t="n">
-        <v>6910028</v>
+        <v>6909922</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124256127</v>
+        <v>124257082</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1461,17 +1456,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498375</v>
+        <v>498617</v>
       </c>
       <c r="R9" t="n">
-        <v>6909917</v>
+        <v>6909667</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,7 +1534,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124256321</v>
+        <v>124255787</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1565,7 +1569,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1579,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498379</v>
+        <v>498444</v>
       </c>
       <c r="R10" t="n">
-        <v>6909903</v>
+        <v>6910034</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124258627</v>
+        <v>124255681</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,31 +1657,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1686,13 +1694,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498669</v>
+        <v>498428</v>
       </c>
       <c r="R11" t="n">
-        <v>6909943</v>
+        <v>6910043</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124257030</v>
+        <v>124256321</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1783,7 +1791,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1793,14 +1801,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498590</v>
+        <v>498379</v>
       </c>
       <c r="R12" t="n">
-        <v>6909676</v>
+        <v>6909903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1859,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124255681</v>
+        <v>124258047</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1871,47 +1879,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498428</v>
+        <v>498617</v>
       </c>
       <c r="R13" t="n">
-        <v>6910043</v>
+        <v>6909667</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124258267</v>
+        <v>124255718</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,38 +1991,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498730</v>
+        <v>498428</v>
       </c>
       <c r="R14" t="n">
-        <v>6909760</v>
+        <v>6910028</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2072,7 +2090,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124257002</v>
+        <v>124256127</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2105,26 +2123,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498588</v>
+        <v>498375</v>
       </c>
       <c r="R15" t="n">
-        <v>6909664</v>
+        <v>6909917</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124255787</v>
+        <v>124255822</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,47 +2204,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498444</v>
+        <v>498423</v>
       </c>
       <c r="R16" t="n">
-        <v>6910034</v>
+        <v>6910002</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124258627</v>
+        <v>124256127</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,46 +800,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498669</v>
+        <v>498375</v>
       </c>
       <c r="R3" t="n">
-        <v>6909943</v>
+        <v>6909917</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124257002</v>
+        <v>124258047</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,35 +902,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498588</v>
+        <v>498617</v>
       </c>
       <c r="R4" t="n">
-        <v>6909664</v>
+        <v>6909667</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1108,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124257030</v>
+        <v>124257002</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1143,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1157,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498590</v>
+        <v>498588</v>
       </c>
       <c r="R6" t="n">
-        <v>6909676</v>
+        <v>6909664</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124256885</v>
+        <v>124257030</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,38 +1227,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498538</v>
+        <v>498590</v>
       </c>
       <c r="R7" t="n">
-        <v>6909687</v>
+        <v>6909676</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124256105</v>
+        <v>124255822</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498395</v>
+        <v>498423</v>
       </c>
       <c r="R8" t="n">
-        <v>6909922</v>
+        <v>6910002</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124257082</v>
+        <v>124256105</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,47 +1440,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498617</v>
+        <v>498395</v>
       </c>
       <c r="R9" t="n">
-        <v>6909667</v>
+        <v>6909922</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1645,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124255681</v>
+        <v>124256321</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1694,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498428</v>
+        <v>498379</v>
       </c>
       <c r="R11" t="n">
-        <v>6910043</v>
+        <v>6909903</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124256321</v>
+        <v>124258627</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,35 +1764,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1805,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498379</v>
+        <v>498669</v>
       </c>
       <c r="R12" t="n">
-        <v>6909903</v>
+        <v>6909943</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124258047</v>
+        <v>124255681</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,48 +1871,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498617</v>
+        <v>498428</v>
       </c>
       <c r="R13" t="n">
-        <v>6909667</v>
+        <v>6910043</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1979,7 +1970,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124255718</v>
+        <v>124257082</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2014,7 +2005,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2024,14 +2015,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498428</v>
+        <v>498617</v>
       </c>
       <c r="R14" t="n">
-        <v>6910028</v>
+        <v>6909667</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2090,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124256127</v>
+        <v>124255718</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2123,17 +2114,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498375</v>
+        <v>498428</v>
       </c>
       <c r="R15" t="n">
-        <v>6909917</v>
+        <v>6910028</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124255822</v>
+        <v>124256885</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498423</v>
+        <v>498538</v>
       </c>
       <c r="R16" t="n">
-        <v>6910002</v>
+        <v>6909687</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124256127</v>
+        <v>124257030</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,17 +821,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498375</v>
+        <v>498590</v>
       </c>
       <c r="R3" t="n">
-        <v>6909917</v>
+        <v>6909676</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124258047</v>
+        <v>124257002</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,36 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -940,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498617</v>
+        <v>498588</v>
       </c>
       <c r="R4" t="n">
-        <v>6909667</v>
+        <v>6909664</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124258267</v>
+        <v>124255822</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1038,14 +1046,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498730</v>
+        <v>498423</v>
       </c>
       <c r="R5" t="n">
-        <v>6909760</v>
+        <v>6910002</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124257002</v>
+        <v>124256127</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1137,26 +1145,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498588</v>
+        <v>498375</v>
       </c>
       <c r="R6" t="n">
-        <v>6909664</v>
+        <v>6909917</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124257030</v>
+        <v>124255718</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1250,7 +1249,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1260,14 +1259,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498590</v>
+        <v>498428</v>
       </c>
       <c r="R7" t="n">
-        <v>6909676</v>
+        <v>6910028</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124255822</v>
+        <v>124258047</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,34 +1341,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498423</v>
+        <v>498617</v>
       </c>
       <c r="R8" t="n">
-        <v>6910002</v>
+        <v>6909667</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124256105</v>
+        <v>124255787</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,38 +1449,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498395</v>
+        <v>498444</v>
       </c>
       <c r="R9" t="n">
-        <v>6909922</v>
+        <v>6910034</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124255787</v>
+        <v>124256105</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,47 +1560,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498444</v>
+        <v>498395</v>
       </c>
       <c r="R10" t="n">
-        <v>6910034</v>
+        <v>6909922</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124256321</v>
+        <v>124258627</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,35 +1662,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1690,13 +1695,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498379</v>
+        <v>498669</v>
       </c>
       <c r="R11" t="n">
-        <v>6909903</v>
+        <v>6909943</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124258627</v>
+        <v>124257082</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,46 +1769,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498669</v>
+        <v>498617</v>
       </c>
       <c r="R12" t="n">
-        <v>6909943</v>
+        <v>6909667</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1868,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124255681</v>
+        <v>124256321</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1908,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498428</v>
+        <v>498379</v>
       </c>
       <c r="R13" t="n">
-        <v>6910043</v>
+        <v>6909903</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124257082</v>
+        <v>124258267</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,47 +1991,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498617</v>
+        <v>498730</v>
       </c>
       <c r="R14" t="n">
-        <v>6909667</v>
+        <v>6909760</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124255718</v>
+        <v>124256885</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,47 +2093,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498428</v>
+        <v>498538</v>
       </c>
       <c r="R15" t="n">
-        <v>6910028</v>
+        <v>6909687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2192,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124256885</v>
+        <v>124255681</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,38 +2195,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498538</v>
+        <v>498428</v>
       </c>
       <c r="R16" t="n">
-        <v>6909687</v>
+        <v>6910043</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124255822</v>
+        <v>124257082</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,38 +1022,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498423</v>
+        <v>498617</v>
       </c>
       <c r="R5" t="n">
-        <v>6910002</v>
+        <v>6909667</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124256127</v>
+        <v>124255681</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1145,17 +1154,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498375</v>
+        <v>498428</v>
       </c>
       <c r="R6" t="n">
-        <v>6909917</v>
+        <v>6910043</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124255718</v>
+        <v>124258627</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,35 +1244,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1263,13 +1277,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498428</v>
+        <v>498669</v>
       </c>
       <c r="R7" t="n">
-        <v>6910028</v>
+        <v>6909943</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124258047</v>
+        <v>124256885</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,44 +1355,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498617</v>
+        <v>498538</v>
       </c>
       <c r="R8" t="n">
-        <v>6909667</v>
+        <v>6909687</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1437,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124255787</v>
+        <v>124255822</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,47 +1453,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498444</v>
+        <v>498423</v>
       </c>
       <c r="R9" t="n">
-        <v>6910034</v>
+        <v>6910002</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124256105</v>
+        <v>124255787</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,38 +1555,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498395</v>
+        <v>498444</v>
       </c>
       <c r="R10" t="n">
-        <v>6909922</v>
+        <v>6910034</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124258627</v>
+        <v>124255718</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,31 +1666,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1695,13 +1703,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498669</v>
+        <v>498428</v>
       </c>
       <c r="R11" t="n">
-        <v>6909943</v>
+        <v>6910028</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124257082</v>
+        <v>124258267</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,47 +1777,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498617</v>
+        <v>498730</v>
       </c>
       <c r="R12" t="n">
-        <v>6909667</v>
+        <v>6909760</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124256321</v>
+        <v>124256127</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1901,26 +1900,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498379</v>
+        <v>498375</v>
       </c>
       <c r="R13" t="n">
-        <v>6909903</v>
+        <v>6909917</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1979,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124258267</v>
+        <v>124258047</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,34 +1985,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498730</v>
+        <v>498617</v>
       </c>
       <c r="R14" t="n">
-        <v>6909760</v>
+        <v>6909667</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124256885</v>
+        <v>124256105</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498538</v>
+        <v>498395</v>
       </c>
       <c r="R15" t="n">
-        <v>6909687</v>
+        <v>6909922</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124255681</v>
+        <v>124256321</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498428</v>
+        <v>498379</v>
       </c>
       <c r="R16" t="n">
-        <v>6910043</v>
+        <v>6909903</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2292,6 +2292,1560 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125294222</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>498858</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6909682</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125293531</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>498712</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6909336</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125294144</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>498894</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6909660</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125293556</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>498719</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6909331</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125293520</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>498688</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6909344</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125294405</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>498579</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6909681</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125294451</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>498585</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6909699</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125294430</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>498567</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6909690</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125293503</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>498685</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6909335</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125294386</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>498580</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6909673</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125294472</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>498591</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6909706</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125294362</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>498585</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6909663</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125294252</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>498853</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6909690</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125293435</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fluganvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>498680</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6909326</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>SCA SCA</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125294222</v>
+        <v>125294451</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498858</v>
+        <v>498585</v>
       </c>
       <c r="R17" t="n">
-        <v>6909682</v>
+        <v>6909699</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125293531</v>
+        <v>125293556</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498712</v>
+        <v>498719</v>
       </c>
       <c r="R18" t="n">
-        <v>6909336</v>
+        <v>6909331</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125294144</v>
+        <v>125293531</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498894</v>
+        <v>498712</v>
       </c>
       <c r="R19" t="n">
-        <v>6909660</v>
+        <v>6909336</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125293556</v>
+        <v>125294252</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498719</v>
+        <v>498853</v>
       </c>
       <c r="R20" t="n">
-        <v>6909331</v>
+        <v>6909690</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125293520</v>
+        <v>125294405</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498688</v>
+        <v>498579</v>
       </c>
       <c r="R21" t="n">
-        <v>6909344</v>
+        <v>6909681</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125294405</v>
+        <v>125294362</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498579</v>
+        <v>498585</v>
       </c>
       <c r="R22" t="n">
-        <v>6909681</v>
+        <v>6909663</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125294451</v>
+        <v>125294472</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498585</v>
+        <v>498591</v>
       </c>
       <c r="R23" t="n">
-        <v>6909699</v>
+        <v>6909706</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125294430</v>
+        <v>125293520</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498567</v>
+        <v>498688</v>
       </c>
       <c r="R24" t="n">
-        <v>6909690</v>
+        <v>6909344</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125293503</v>
+        <v>125294430</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498685</v>
+        <v>498567</v>
       </c>
       <c r="R25" t="n">
-        <v>6909335</v>
+        <v>6909690</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125294386</v>
+        <v>125293503</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>498580</v>
+        <v>498685</v>
       </c>
       <c r="R26" t="n">
-        <v>6909673</v>
+        <v>6909335</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125294472</v>
+        <v>125294386</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498591</v>
+        <v>498580</v>
       </c>
       <c r="R27" t="n">
-        <v>6909706</v>
+        <v>6909673</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125294362</v>
+        <v>125294222</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498585</v>
+        <v>498858</v>
       </c>
       <c r="R28" t="n">
-        <v>6909663</v>
+        <v>6909682</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125294252</v>
+        <v>125294144</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498853</v>
+        <v>498894</v>
       </c>
       <c r="R29" t="n">
-        <v>6909690</v>
+        <v>6909660</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125294451</v>
+        <v>125293520</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498585</v>
+        <v>498688</v>
       </c>
       <c r="R17" t="n">
-        <v>6909699</v>
+        <v>6909344</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125293556</v>
+        <v>125294252</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498719</v>
+        <v>498853</v>
       </c>
       <c r="R18" t="n">
-        <v>6909331</v>
+        <v>6909690</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125293531</v>
+        <v>125294472</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498712</v>
+        <v>498591</v>
       </c>
       <c r="R19" t="n">
-        <v>6909336</v>
+        <v>6909706</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125294252</v>
+        <v>125293556</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498853</v>
+        <v>498719</v>
       </c>
       <c r="R20" t="n">
-        <v>6909690</v>
+        <v>6909331</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125294362</v>
+        <v>125294386</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498585</v>
+        <v>498580</v>
       </c>
       <c r="R22" t="n">
-        <v>6909663</v>
+        <v>6909673</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125294472</v>
+        <v>125294451</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498591</v>
+        <v>498585</v>
       </c>
       <c r="R23" t="n">
-        <v>6909706</v>
+        <v>6909699</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125293520</v>
+        <v>125293435</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498688</v>
+        <v>498680</v>
       </c>
       <c r="R24" t="n">
-        <v>6909344</v>
+        <v>6909326</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125294430</v>
+        <v>125294222</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498567</v>
+        <v>498858</v>
       </c>
       <c r="R25" t="n">
-        <v>6909690</v>
+        <v>6909682</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125293503</v>
+        <v>125294144</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>498685</v>
+        <v>498894</v>
       </c>
       <c r="R26" t="n">
-        <v>6909335</v>
+        <v>6909660</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125294386</v>
+        <v>125293503</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498580</v>
+        <v>498685</v>
       </c>
       <c r="R27" t="n">
-        <v>6909673</v>
+        <v>6909335</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125294222</v>
+        <v>125293531</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498858</v>
+        <v>498712</v>
       </c>
       <c r="R28" t="n">
-        <v>6909682</v>
+        <v>6909336</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125294144</v>
+        <v>125294430</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498894</v>
+        <v>498567</v>
       </c>
       <c r="R29" t="n">
-        <v>6909660</v>
+        <v>6909690</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125293435</v>
+        <v>125294362</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498680</v>
+        <v>498585</v>
       </c>
       <c r="R30" t="n">
-        <v>6909326</v>
+        <v>6909663</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125293520</v>
+        <v>125293556</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498688</v>
+        <v>498719</v>
       </c>
       <c r="R17" t="n">
-        <v>6909344</v>
+        <v>6909331</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125294252</v>
+        <v>125293531</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498853</v>
+        <v>498712</v>
       </c>
       <c r="R18" t="n">
-        <v>6909690</v>
+        <v>6909336</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125294472</v>
+        <v>125293435</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498591</v>
+        <v>498680</v>
       </c>
       <c r="R19" t="n">
-        <v>6909706</v>
+        <v>6909326</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125293556</v>
+        <v>125293520</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498719</v>
+        <v>498688</v>
       </c>
       <c r="R20" t="n">
-        <v>6909331</v>
+        <v>6909344</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125294405</v>
+        <v>125293503</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498579</v>
+        <v>498685</v>
       </c>
       <c r="R21" t="n">
-        <v>6909681</v>
+        <v>6909335</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125294386</v>
+        <v>125294362</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498580</v>
+        <v>498585</v>
       </c>
       <c r="R22" t="n">
-        <v>6909673</v>
+        <v>6909663</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125294451</v>
+        <v>125294472</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498585</v>
+        <v>498591</v>
       </c>
       <c r="R23" t="n">
-        <v>6909699</v>
+        <v>6909706</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125293435</v>
+        <v>125294386</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498680</v>
+        <v>498580</v>
       </c>
       <c r="R24" t="n">
-        <v>6909326</v>
+        <v>6909673</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125294222</v>
+        <v>125294430</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498858</v>
+        <v>498567</v>
       </c>
       <c r="R25" t="n">
-        <v>6909682</v>
+        <v>6909690</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125294144</v>
+        <v>125294451</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>498894</v>
+        <v>498585</v>
       </c>
       <c r="R26" t="n">
-        <v>6909660</v>
+        <v>6909699</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125293503</v>
+        <v>125294252</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498685</v>
+        <v>498853</v>
       </c>
       <c r="R27" t="n">
-        <v>6909335</v>
+        <v>6909690</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125293531</v>
+        <v>125294144</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498712</v>
+        <v>498894</v>
       </c>
       <c r="R28" t="n">
-        <v>6909336</v>
+        <v>6909660</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125294430</v>
+        <v>125294222</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498567</v>
+        <v>498858</v>
       </c>
       <c r="R29" t="n">
-        <v>6909690</v>
+        <v>6909682</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125294362</v>
+        <v>125294405</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498585</v>
+        <v>498579</v>
       </c>
       <c r="R30" t="n">
-        <v>6909663</v>
+        <v>6909681</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125293556</v>
+        <v>125294430</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498719</v>
+        <v>498567</v>
       </c>
       <c r="R17" t="n">
-        <v>6909331</v>
+        <v>6909690</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125293531</v>
+        <v>125293435</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498712</v>
+        <v>498680</v>
       </c>
       <c r="R18" t="n">
-        <v>6909336</v>
+        <v>6909326</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125293435</v>
+        <v>125294386</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498680</v>
+        <v>498580</v>
       </c>
       <c r="R19" t="n">
-        <v>6909326</v>
+        <v>6909673</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125293520</v>
+        <v>125294451</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498688</v>
+        <v>498585</v>
       </c>
       <c r="R20" t="n">
-        <v>6909344</v>
+        <v>6909699</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125293503</v>
+        <v>125294222</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498685</v>
+        <v>498858</v>
       </c>
       <c r="R21" t="n">
-        <v>6909335</v>
+        <v>6909682</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125294362</v>
+        <v>125294144</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498585</v>
+        <v>498894</v>
       </c>
       <c r="R22" t="n">
-        <v>6909663</v>
+        <v>6909660</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125294472</v>
+        <v>125293556</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498591</v>
+        <v>498719</v>
       </c>
       <c r="R23" t="n">
-        <v>6909706</v>
+        <v>6909331</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125294386</v>
+        <v>125294472</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498580</v>
+        <v>498591</v>
       </c>
       <c r="R24" t="n">
-        <v>6909673</v>
+        <v>6909706</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125294430</v>
+        <v>125293520</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498567</v>
+        <v>498688</v>
       </c>
       <c r="R25" t="n">
-        <v>6909690</v>
+        <v>6909344</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125294451</v>
+        <v>125294362</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
         <v>498585</v>
       </c>
       <c r="R26" t="n">
-        <v>6909699</v>
+        <v>6909663</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125294252</v>
+        <v>125293531</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498853</v>
+        <v>498712</v>
       </c>
       <c r="R27" t="n">
-        <v>6909690</v>
+        <v>6909336</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125294144</v>
+        <v>125294405</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498894</v>
+        <v>498579</v>
       </c>
       <c r="R28" t="n">
-        <v>6909660</v>
+        <v>6909681</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125294222</v>
+        <v>125294252</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498858</v>
+        <v>498853</v>
       </c>
       <c r="R29" t="n">
-        <v>6909682</v>
+        <v>6909690</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125294405</v>
+        <v>125293503</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498579</v>
+        <v>498685</v>
       </c>
       <c r="R30" t="n">
-        <v>6909681</v>
+        <v>6909335</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125294430</v>
+        <v>125294222</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498567</v>
+        <v>498858</v>
       </c>
       <c r="R17" t="n">
-        <v>6909690</v>
+        <v>6909682</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125293435</v>
+        <v>125294451</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498680</v>
+        <v>498585</v>
       </c>
       <c r="R18" t="n">
-        <v>6909326</v>
+        <v>6909699</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125294386</v>
+        <v>125293503</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498580</v>
+        <v>498685</v>
       </c>
       <c r="R19" t="n">
-        <v>6909673</v>
+        <v>6909335</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125294451</v>
+        <v>125293531</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498585</v>
+        <v>498712</v>
       </c>
       <c r="R20" t="n">
-        <v>6909699</v>
+        <v>6909336</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125294222</v>
+        <v>125293556</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498858</v>
+        <v>498719</v>
       </c>
       <c r="R21" t="n">
-        <v>6909682</v>
+        <v>6909331</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125294144</v>
+        <v>125294472</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498894</v>
+        <v>498591</v>
       </c>
       <c r="R22" t="n">
-        <v>6909660</v>
+        <v>6909706</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125293556</v>
+        <v>125294252</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498719</v>
+        <v>498853</v>
       </c>
       <c r="R23" t="n">
-        <v>6909331</v>
+        <v>6909690</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,10 +3071,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125294472</v>
+        <v>125294144</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498591</v>
+        <v>498894</v>
       </c>
       <c r="R24" t="n">
-        <v>6909706</v>
+        <v>6909660</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125293520</v>
+        <v>125294430</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498688</v>
+        <v>498567</v>
       </c>
       <c r="R25" t="n">
-        <v>6909344</v>
+        <v>6909690</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3296,7 +3296,7 @@
         <v>125294362</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125293531</v>
+        <v>125293520</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498712</v>
+        <v>498688</v>
       </c>
       <c r="R27" t="n">
-        <v>6909336</v>
+        <v>6909344</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125294405</v>
+        <v>125294386</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498579</v>
+        <v>498580</v>
       </c>
       <c r="R28" t="n">
-        <v>6909681</v>
+        <v>6909673</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125294252</v>
+        <v>125294405</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498853</v>
+        <v>498579</v>
       </c>
       <c r="R29" t="n">
-        <v>6909690</v>
+        <v>6909681</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125293503</v>
+        <v>125293435</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498685</v>
+        <v>498680</v>
       </c>
       <c r="R30" t="n">
-        <v>6909335</v>
+        <v>6909326</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -2294,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125294222</v>
+        <v>125293531</v>
       </c>
       <c r="B17" t="n">
         <v>98269</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498858</v>
+        <v>498712</v>
       </c>
       <c r="R17" t="n">
-        <v>6909682</v>
+        <v>6909336</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125294451</v>
+        <v>125294252</v>
       </c>
       <c r="B18" t="n">
         <v>98269</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498585</v>
+        <v>498853</v>
       </c>
       <c r="R18" t="n">
-        <v>6909699</v>
+        <v>6909690</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125293503</v>
+        <v>125294222</v>
       </c>
       <c r="B19" t="n">
         <v>98269</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498685</v>
+        <v>498858</v>
       </c>
       <c r="R19" t="n">
-        <v>6909335</v>
+        <v>6909682</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125293531</v>
+        <v>125293556</v>
       </c>
       <c r="B20" t="n">
         <v>98269</v>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498712</v>
+        <v>498719</v>
       </c>
       <c r="R20" t="n">
-        <v>6909336</v>
+        <v>6909331</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125293556</v>
+        <v>125293503</v>
       </c>
       <c r="B21" t="n">
         <v>98269</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498719</v>
+        <v>498685</v>
       </c>
       <c r="R21" t="n">
-        <v>6909331</v>
+        <v>6909335</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125294472</v>
+        <v>125293520</v>
       </c>
       <c r="B22" t="n">
         <v>98269</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498591</v>
+        <v>498688</v>
       </c>
       <c r="R22" t="n">
-        <v>6909706</v>
+        <v>6909344</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125294252</v>
+        <v>125294451</v>
       </c>
       <c r="B23" t="n">
         <v>98269</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498853</v>
+        <v>498585</v>
       </c>
       <c r="R23" t="n">
-        <v>6909690</v>
+        <v>6909699</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125294144</v>
+        <v>125293435</v>
       </c>
       <c r="B24" t="n">
         <v>98269</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498894</v>
+        <v>498680</v>
       </c>
       <c r="R24" t="n">
-        <v>6909660</v>
+        <v>6909326</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125294430</v>
+        <v>125294386</v>
       </c>
       <c r="B25" t="n">
         <v>98269</v>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498567</v>
+        <v>498580</v>
       </c>
       <c r="R25" t="n">
-        <v>6909690</v>
+        <v>6909673</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125294362</v>
+        <v>125294144</v>
       </c>
       <c r="B26" t="n">
         <v>98269</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>498585</v>
+        <v>498894</v>
       </c>
       <c r="R26" t="n">
-        <v>6909663</v>
+        <v>6909660</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125293520</v>
+        <v>125294405</v>
       </c>
       <c r="B27" t="n">
         <v>98269</v>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498688</v>
+        <v>498579</v>
       </c>
       <c r="R27" t="n">
-        <v>6909344</v>
+        <v>6909681</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125294386</v>
+        <v>125294362</v>
       </c>
       <c r="B28" t="n">
         <v>98269</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498580</v>
+        <v>498585</v>
       </c>
       <c r="R28" t="n">
-        <v>6909673</v>
+        <v>6909663</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125294405</v>
+        <v>125294472</v>
       </c>
       <c r="B29" t="n">
         <v>98269</v>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498579</v>
+        <v>498591</v>
       </c>
       <c r="R29" t="n">
-        <v>6909681</v>
+        <v>6909706</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125293435</v>
+        <v>125294430</v>
       </c>
       <c r="B30" t="n">
         <v>98269</v>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498680</v>
+        <v>498567</v>
       </c>
       <c r="R30" t="n">
-        <v>6909326</v>
+        <v>6909690</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -2294,15 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125293531</v>
+        <v>125294222</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2324,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2342,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498712</v>
+        <v>498858</v>
       </c>
       <c r="R17" t="n">
-        <v>6909336</v>
+        <v>6909682</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,15 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125294252</v>
+        <v>125293503</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2430,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2453,10 +2443,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498853</v>
+        <v>498685</v>
       </c>
       <c r="R18" t="n">
-        <v>6909690</v>
+        <v>6909335</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,15 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125294222</v>
+        <v>125293531</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2536,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2564,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498858</v>
+        <v>498712</v>
       </c>
       <c r="R19" t="n">
-        <v>6909682</v>
+        <v>6909336</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,15 +2612,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125293556</v>
+        <v>125294405</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498719</v>
+        <v>498579</v>
       </c>
       <c r="R20" t="n">
-        <v>6909331</v>
+        <v>6909681</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,15 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125293503</v>
+        <v>125294451</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,7 +2748,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2786,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498685</v>
+        <v>498585</v>
       </c>
       <c r="R21" t="n">
-        <v>6909335</v>
+        <v>6909699</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2849,15 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125293520</v>
+        <v>125293556</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498688</v>
+        <v>498719</v>
       </c>
       <c r="R22" t="n">
-        <v>6909344</v>
+        <v>6909331</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,15 +2930,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125294451</v>
+        <v>125293520</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,7 +2960,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3008,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498585</v>
+        <v>498688</v>
       </c>
       <c r="R23" t="n">
-        <v>6909699</v>
+        <v>6909344</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3071,15 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125293435</v>
+        <v>125294472</v>
       </c>
       <c r="B24" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3066,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3119,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498680</v>
+        <v>498591</v>
       </c>
       <c r="R24" t="n">
-        <v>6909326</v>
+        <v>6909706</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3185,12 +3145,7 @@
         <v>125294386</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,12 +3251,7 @@
         <v>125294144</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3404,15 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125294405</v>
+        <v>125294252</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3439,7 +3384,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3452,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498579</v>
+        <v>498853</v>
       </c>
       <c r="R27" t="n">
-        <v>6909681</v>
+        <v>6909690</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3515,15 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125294362</v>
+        <v>125293435</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3550,7 +3490,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3563,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498585</v>
+        <v>498680</v>
       </c>
       <c r="R28" t="n">
-        <v>6909663</v>
+        <v>6909326</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3626,15 +3566,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125294472</v>
+        <v>125294430</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3596,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3674,10 +3609,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498591</v>
+        <v>498567</v>
       </c>
       <c r="R29" t="n">
-        <v>6909706</v>
+        <v>6909690</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3737,15 +3672,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125294430</v>
+        <v>125294362</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3772,7 +3702,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3785,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498567</v>
+        <v>498585</v>
       </c>
       <c r="R30" t="n">
-        <v>6909690</v>
+        <v>6909663</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -2297,7 +2297,7 @@
         <v>125294222</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>125293503</v>
       </c>
       <c r="B18" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>125293531</v>
       </c>
       <c r="B19" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>125294405</v>
       </c>
       <c r="B20" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>125294451</v>
       </c>
       <c r="B21" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>125293556</v>
       </c>
       <c r="B22" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>125293520</v>
       </c>
       <c r="B23" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>125294472</v>
       </c>
       <c r="B24" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>125294386</v>
       </c>
       <c r="B25" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>125294144</v>
       </c>
       <c r="B26" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>125294252</v>
       </c>
       <c r="B27" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>125293435</v>
       </c>
       <c r="B28" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>125294430</v>
       </c>
       <c r="B29" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>125294362</v>
       </c>
       <c r="B30" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -2297,7 +2297,7 @@
         <v>125294222</v>
       </c>
       <c r="B17" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>125293503</v>
       </c>
       <c r="B18" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>125293531</v>
       </c>
       <c r="B19" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>125294405</v>
       </c>
       <c r="B20" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>125294451</v>
       </c>
       <c r="B21" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>125293556</v>
       </c>
       <c r="B22" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>125293520</v>
       </c>
       <c r="B23" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>125294472</v>
       </c>
       <c r="B24" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>125294386</v>
       </c>
       <c r="B25" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>125294144</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>125294252</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>125293435</v>
       </c>
       <c r="B28" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>125294430</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>125294362</v>
       </c>
       <c r="B30" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -1235,12 +1235,7 @@
         <v>124258627</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>124258627</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>124258627</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19010-2025 artfynd.xlsx
+++ b/artfynd/A 19010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104453052</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124255822</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124256885</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124258267</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124258627</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124258047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124255681</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124255718</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124255787</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124256127</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1801,6 +1856,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124256321</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,6 +1967,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124257002</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124257030</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124257082</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2225,6 +2300,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125293435</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2331,6 +2411,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125293503</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2437,6 +2522,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125293520</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2543,6 +2633,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125293531</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2649,6 +2744,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125293556</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2755,6 +2855,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294144</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2861,6 +2966,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294222</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2967,6 +3077,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294252</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3073,6 +3188,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294362</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3179,6 +3299,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294386</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3285,6 +3410,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294405</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3391,6 +3521,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294430</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3497,6 +3632,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294451</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3603,6 +3743,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294472</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3700,8 +3845,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124256105</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>